--- a/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-5.xlsx
+++ b/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\App_Uv\AppAcompanhamientoUV\Doc_Test\Pruebas_Calidad\Pruebas_Unitarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF21DF56-96C3-4410-82E1-8A81231AB57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51890498-A8DC-4E98-B595-EF8C6C8B0551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2FFDA8E8-6428-4D51-9D6D-F314F8731DBF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -221,9 +221,6 @@
     <t>CP-2.5</t>
   </si>
   <si>
-    <t>Probar Registrar un estado excelente sin complementos opcionales (Dispositivo físico)</t>
-  </si>
-  <si>
     <t>CP-3</t>
   </si>
   <si>
@@ -234,6 +231,9 @@
   </si>
   <si>
     <t>(1) Se le debe permitir al usuario ingresar uno o más estados de ánimo.                                                                                                    (2) Al finalizar el registro se le debe mostrar un consejo retroalimentativo dependiendo de su estado de ánimo.                                   (3) Se debe mostrar el estado registrado en la pestaña de inicio.</t>
+  </si>
+  <si>
+    <t>Probar Registrar un estado "Mal" sin complementos opcionales (Dispositivo físico)</t>
   </si>
 </sst>
 </file>
@@ -421,6 +421,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -439,15 +440,24 @@
     <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -466,16 +476,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,135 +831,135 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="2:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>45848</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" spans="2:14" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
+      <c r="C9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="2:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
@@ -986,23 +986,23 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
     </row>
     <row r="12" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="27"/>
+      <c r="B12" s="19"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -1021,18 +1021,18 @@
       <c r="H12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="27"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
@@ -1048,14 +1048,16 @@
       <c r="G13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="24"/>
-      <c r="N13" s="29"/>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="28"/>
+      <c r="N13" s="11"/>
     </row>
     <row r="14" spans="2:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="B14" s="27"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="9" t="s">
         <v>18</v>
       </c>
@@ -1074,12 +1076,12 @@
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="24"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" spans="2:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="9" t="s">
         <v>51</v>
       </c>
@@ -1098,28 +1100,28 @@
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="29"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
     </row>
     <row r="17" spans="2:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="17"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="7" t="s">
         <v>24</v>
       </c>
@@ -1138,18 +1140,18 @@
       <c r="H17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="17"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="7" t="s">
         <v>25</v>
       </c>
@@ -1165,13 +1167,15 @@
       <c r="G18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="18"/>
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="21"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="21"/>
     </row>
     <row r="19" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B19" s="17"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="7" t="s">
         <v>26</v>
       </c>
@@ -1190,12 +1194,12 @@
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="18"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="21"/>
     </row>
     <row r="20" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B20" s="17"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="7" t="s">
         <v>59</v>
       </c>
@@ -1214,12 +1218,12 @@
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="18"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="21"/>
     </row>
     <row r="21" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B21" s="17"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="7" t="s">
         <v>60</v>
       </c>
@@ -1238,30 +1242,30 @@
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="18"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B23" s="23"/>
+      <c r="C23" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-    </row>
-    <row r="23" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="17"/>
-      <c r="C23" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>33</v>
@@ -1278,18 +1282,18 @@
       <c r="H23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="19" t="s">
+      <c r="J23" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="18"/>
+      <c r="K23" s="21"/>
     </row>
     <row r="24" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B24" s="17"/>
+      <c r="B24" s="23"/>
       <c r="C24" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
@@ -1306,9 +1310,9 @@
       <c r="H24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="18"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="24">
